--- a/tests/modern_sulfur_cycle/reaction_network.xlsx
+++ b/tests/modern_sulfur_cycle/reaction_network.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1221e7247ec036c5/学术会议/25_10_31 PATMO workshop/Modern sulfur cycle/input files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrick/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="446" documentId="13_ncr:1_{6691F15E-43E2-8B40-B489-DEA076D9154A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42B2622A-968A-48DC-8B73-ACCC83F5FEE2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD03B70-3498-994E-AE76-8878503B061A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10780" yWindow="240" windowWidth="23280" windowHeight="18670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10780" yWindow="760" windowWidth="23280" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -114,10 +114,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>(1.25E-16*exp(4550/T))/(T+1.81*10**(-3)*exp(3400/T))</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>3.2E-11*exp(-650/T)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -259,6 +255,10 @@
   </si>
   <si>
     <t>CS2E</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1.25E-16*exp(4550/T))/(T+(1.81E-3)*exp(3400/T))</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -266,7 +266,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,7 +339,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -358,10 +358,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -645,13 +641,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="30" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -677,7 +673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -688,16 +684,16 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -714,10 +710,10 @@
         <v>16</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -737,7 +733,7 @@
         <v>2.0000000000000002E-15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -754,10 +750,10 @@
         <v>16</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -774,10 +770,10 @@
         <v>17</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -794,10 +790,10 @@
         <v>19</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -811,10 +807,10 @@
         <v>14</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -834,7 +830,7 @@
         <v>2.8000000000000001E-14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -851,10 +847,10 @@
         <v>19</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -874,7 +870,7 @@
         <v>2.9E-19</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -894,7 +890,7 @@
         <v>2.9E-20</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -914,32 +910,32 @@
         <v>2.9999999999999999E-16</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
@@ -951,21 +947,21 @@
         <v>13</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
@@ -974,27 +970,27 @@
         <v>8.0000000000000002E-13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
         <v>36</v>
       </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>37</v>
-      </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H17" s="5">
         <v>2.9999999999999998E-15</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1008,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H18" s="5">
         <v>1.5999999999999999E-10</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1034,7 +1030,7 @@
         <v>3.9999999999999999E-19</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1045,16 +1041,16 @@
         <v>6</v>
       </c>
       <c r="E20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F20" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1071,10 +1067,10 @@
         <v>4</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1091,10 +1087,10 @@
         <v>5</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1108,13 +1104,13 @@
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1131,10 +1127,10 @@
         <v>4</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1154,7 +1150,7 @@
         <v>1.2000000000000001E-11</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1168,36 +1164,36 @@
         <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H26" s="5">
         <v>6.6000000000000005E-11</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1205,19 +1201,19 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H28" s="5">
         <v>1.0000000000000001E-18</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1231,18 +1227,18 @@
         <v>5</v>
       </c>
       <c r="F29" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H29" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -1257,12 +1253,12 @@
         <v>2.0000000000000001E-17</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>6</v>
@@ -1281,7 +1277,7 @@
         <v>1E-13</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1295,33 +1291,33 @@
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H32" s="5">
         <v>2.9999999999999998E-13</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" t="s">
+        <v>40</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C33" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" t="s">
-        <v>32</v>
-      </c>
-      <c r="F33" t="s">
-        <v>41</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1332,36 +1328,36 @@
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H35" s="5">
         <v>1.2E-15</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1378,7 +1374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1386,16 +1382,16 @@
         <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H37" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1403,18 +1399,18 @@
         <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H38" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
@@ -1423,15 +1419,15 @@
         <v>10</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
@@ -1440,15 +1436,15 @@
         <v>10</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
@@ -1457,13 +1453,13 @@
         <v>10</v>
       </c>
       <c r="F41" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H41" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -1483,32 +1479,32 @@
         <v>1.6E-13</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H43" s="4">
         <v>2.5000000000000001E-11</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -1523,7 +1519,7 @@
         <v>1.2499999999999999E-12</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="16" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -1533,7 +1529,7 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -1543,7 +1539,7 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
